--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:38</t>
+    <t xml:space="preserve">2026-09-09 19:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:57</t>
+    <t xml:space="preserve">2026-09-18 17:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
@@ -30,102 +30,102 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curarrehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pucón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traiguén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ercilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacautín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lautaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorbea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saavedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galvarino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loncoche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teodoro Schmidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholchol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholchol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teodoro Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loncoche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galvarino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saavedra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorbea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lautaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacautín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ercilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiguén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cunco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pucón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curarrehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:03</t>
+    <t xml:space="preserve">2026-09-27 21:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -555,13 +555,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9136</v>
+        <v>6783</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10076</v>
+        <v>6239</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>90.67</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="3">
@@ -569,13 +569,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>75848</v>
+        <v>63478</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>81101</v>
+        <v>58574</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>93.52</v>
+        <v>108.37</v>
       </c>
     </row>
     <row r="4">
@@ -583,13 +583,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>28506</v>
+        <v>8257</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>30253</v>
+        <v>7767</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.23</v>
+        <v>106.31</v>
       </c>
     </row>
     <row r="5">
@@ -597,13 +597,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11706</v>
+        <v>31008</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12237</v>
+        <v>29469</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95.66</v>
+        <v>105.22</v>
       </c>
     </row>
     <row r="6">
@@ -611,13 +611,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>288737</v>
+        <v>12803</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>300618</v>
+        <v>12192</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>96.05</v>
+        <v>105.01</v>
       </c>
     </row>
     <row r="7">
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>15163</v>
+        <v>18817</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>15771</v>
+        <v>18030</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>96.14</v>
+        <v>104.36</v>
       </c>
     </row>
     <row r="8">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>23780</v>
+        <v>19997</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>24684</v>
+        <v>19306</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>96.34</v>
+        <v>103.58</v>
       </c>
     </row>
     <row r="9">
@@ -653,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7298</v>
+        <v>8706</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7516</v>
+        <v>8468</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>97.1</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="10">
@@ -667,13 +667,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>24873</v>
+        <v>57107</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25391</v>
+        <v>55761</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>97.96</v>
+        <v>102.41</v>
       </c>
     </row>
     <row r="11">
@@ -681,13 +681,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12440</v>
+        <v>18466</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12630</v>
+        <v>18137</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>98.5</v>
+        <v>101.81</v>
       </c>
     </row>
     <row r="12">
@@ -695,13 +695,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10867</v>
+        <v>34156</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>11014</v>
+        <v>33614</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>98.67</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="13">
@@ -709,13 +709,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10631</v>
+        <v>26118</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10764</v>
+        <v>25996</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>98.76</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="14">
@@ -723,13 +723,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12672</v>
+        <v>35493</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12812</v>
+        <v>35393</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>98.91</v>
+        <v>100.28</v>
       </c>
     </row>
     <row r="15">
@@ -737,13 +737,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>25740</v>
+        <v>25481</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>25916</v>
+        <v>25444</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>99.32</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="16">
@@ -751,13 +751,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7154</v>
+        <v>40402</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7197</v>
+        <v>40376</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>99.4</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="17">
@@ -765,13 +765,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10046</v>
+        <v>15144</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10075</v>
+        <v>15144</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>99.71</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -779,13 +779,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>15144</v>
+        <v>10046</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>15144</v>
+        <v>10075</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>100</v>
+        <v>99.71</v>
       </c>
     </row>
     <row r="19">
@@ -793,13 +793,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>40402</v>
+        <v>7154</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>40376</v>
+        <v>7197</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>100.06</v>
+        <v>99.4</v>
       </c>
     </row>
     <row r="20">
@@ -807,13 +807,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>25481</v>
+        <v>25740</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>25444</v>
+        <v>25916</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>100.15</v>
+        <v>99.32</v>
       </c>
     </row>
     <row r="21">
@@ -821,13 +821,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>35493</v>
+        <v>12672</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>35393</v>
+        <v>12812</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>100.28</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="22">
@@ -835,13 +835,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>26118</v>
+        <v>10631</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>25996</v>
+        <v>10764</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>100.47</v>
+        <v>98.76</v>
       </c>
     </row>
     <row r="23">
@@ -849,13 +849,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>34156</v>
+        <v>10867</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>33614</v>
+        <v>11014</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>101.61</v>
+        <v>98.67</v>
       </c>
     </row>
     <row r="24">
@@ -863,13 +863,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>18466</v>
+        <v>12440</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>18137</v>
+        <v>12630</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>101.81</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="25">
@@ -877,13 +877,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>57107</v>
+        <v>24873</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>55761</v>
+        <v>25391</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>102.41</v>
+        <v>97.96</v>
       </c>
     </row>
     <row r="26">
@@ -891,13 +891,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8706</v>
+        <v>7298</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8468</v>
+        <v>7516</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>102.81</v>
+        <v>97.1</v>
       </c>
     </row>
     <row r="27">
@@ -905,13 +905,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>19997</v>
+        <v>23780</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>19306</v>
+        <v>24684</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>103.58</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="28">
@@ -919,13 +919,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>18817</v>
+        <v>15163</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>18030</v>
+        <v>15771</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>104.36</v>
+        <v>96.14</v>
       </c>
     </row>
     <row r="29">
@@ -933,13 +933,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>12803</v>
+        <v>288737</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>12192</v>
+        <v>300618</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>105.01</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="30">
@@ -947,13 +947,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>31008</v>
+        <v>11706</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>29469</v>
+        <v>12237</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>105.22</v>
+        <v>95.66</v>
       </c>
     </row>
     <row r="31">
@@ -961,13 +961,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>8257</v>
+        <v>28506</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7767</v>
+        <v>30253</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>106.31</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="32">
@@ -975,13 +975,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>63478</v>
+        <v>75848</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>58574</v>
+        <v>81101</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>108.37</v>
+        <v>93.52</v>
       </c>
     </row>
     <row r="33">
@@ -989,13 +989,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>6783</v>
+        <v>9136</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6239</v>
+        <v>10076</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>108.72</v>
+        <v>90.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_la_araucania.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:45</t>
+    <t xml:space="preserve">2026-10-05 05:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
